--- a/Analysis/power_budget.xlsx
+++ b/Analysis/power_budget.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\kicad_designs\ADAU1450\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\kicad_designs\ADAU1450\Github\Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12435" firstSheet="2" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12435" firstSheet="2" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Power Budget" sheetId="1" state="hidden" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="262">
   <si>
     <t>Power Budget</t>
   </si>
@@ -286,9 +286,6 @@
     <t>Unreg 5V</t>
   </si>
   <si>
-    <t>Multipurpose</t>
-  </si>
-  <si>
     <t>MP0</t>
   </si>
   <si>
@@ -325,96 +322,12 @@
     <t>MP11</t>
   </si>
   <si>
-    <t>ADC1</t>
-  </si>
-  <si>
-    <t>ADC2</t>
-  </si>
-  <si>
-    <t>ADC3</t>
-  </si>
-  <si>
-    <t>ADC0</t>
-  </si>
-  <si>
     <t>Use</t>
   </si>
   <si>
-    <t>POT1</t>
-  </si>
-  <si>
-    <t>POT2</t>
-  </si>
-  <si>
-    <t>POT3</t>
-  </si>
-  <si>
-    <t>POT0</t>
-  </si>
-  <si>
-    <t>SDATA_IN0 / tdm_IN</t>
-  </si>
-  <si>
     <t>SDATA_IN1</t>
   </si>
   <si>
-    <t>Serial Data</t>
-  </si>
-  <si>
-    <t>Analog</t>
-  </si>
-  <si>
-    <t>SDATA_IN2</t>
-  </si>
-  <si>
-    <t>SDATA_IN3</t>
-  </si>
-  <si>
-    <t>INPUT_LRCLK</t>
-  </si>
-  <si>
-    <t>INPUT_BCLK</t>
-  </si>
-  <si>
-    <t>SDATA_OUT0 / TDM_OUT</t>
-  </si>
-  <si>
-    <t>SDATA_OUT1</t>
-  </si>
-  <si>
-    <t>SDATA_OUT2</t>
-  </si>
-  <si>
-    <t>SDATA_OUT3</t>
-  </si>
-  <si>
-    <t>OUTPUT_LRCLK</t>
-  </si>
-  <si>
-    <t>OUTPUT_BCLK</t>
-  </si>
-  <si>
-    <t>OUTPUT_LRCK</t>
-  </si>
-  <si>
-    <t>OUTPUT_BCK</t>
-  </si>
-  <si>
-    <t>DATA_OUT</t>
-  </si>
-  <si>
-    <t>DATA_IN</t>
-  </si>
-  <si>
-    <t>INPUT_LRCK</t>
-  </si>
-  <si>
-    <t>INPUT_BCK</t>
-  </si>
-  <si>
-    <t>Pushbutton</t>
-  </si>
-  <si>
     <t>V_NRSS</t>
   </si>
   <si>
@@ -623,6 +536,285 @@
   </si>
   <si>
     <t>ADAU1450 (DSP)</t>
+  </si>
+  <si>
+    <t>AUXADC0</t>
+  </si>
+  <si>
+    <t>AUXADC1</t>
+  </si>
+  <si>
+    <t>AUXADC2</t>
+  </si>
+  <si>
+    <t>AUXADC3</t>
+  </si>
+  <si>
+    <t>POT 1</t>
+  </si>
+  <si>
+    <t>POT 2</t>
+  </si>
+  <si>
+    <t>POT 3</t>
+  </si>
+  <si>
+    <t>POT 4</t>
+  </si>
+  <si>
+    <t>AUXADC4</t>
+  </si>
+  <si>
+    <t>AUXADC5</t>
+  </si>
+  <si>
+    <t>NC</t>
+  </si>
+  <si>
+    <t>ADAU1450 Signal</t>
+  </si>
+  <si>
+    <t>BCLK_IN0</t>
+  </si>
+  <si>
+    <t>LRCLK_IN0</t>
+  </si>
+  <si>
+    <t>SDATA_IN0</t>
+  </si>
+  <si>
+    <t>BCLK_IN1</t>
+  </si>
+  <si>
+    <t>LRCLK_IN1</t>
+  </si>
+  <si>
+    <t>ADC_BICK</t>
+  </si>
+  <si>
+    <t>ADC_LRCK</t>
+  </si>
+  <si>
+    <t>ADC_DATA</t>
+  </si>
+  <si>
+    <t>YORK_BCK</t>
+  </si>
+  <si>
+    <t>YORK_LRCK</t>
+  </si>
+  <si>
+    <t>YORK_DATA</t>
+  </si>
+  <si>
+    <t>LRCLK_OUT0</t>
+  </si>
+  <si>
+    <t>BCLK_OUT0</t>
+  </si>
+  <si>
+    <t>SDATA_OUT0</t>
+  </si>
+  <si>
+    <t>DAC_LRCK</t>
+  </si>
+  <si>
+    <t>DAC_BICK</t>
+  </si>
+  <si>
+    <t>DAC_DATA</t>
+  </si>
+  <si>
+    <t>MP12</t>
+  </si>
+  <si>
+    <t>MP13</t>
+  </si>
+  <si>
+    <t>EEPROM_SS</t>
+  </si>
+  <si>
+    <t>SS_M</t>
+  </si>
+  <si>
+    <t>EEPRON_MOSI</t>
+  </si>
+  <si>
+    <t>MOSI_M</t>
+  </si>
+  <si>
+    <t>EEPRON_SCLK</t>
+  </si>
+  <si>
+    <t>SCLK_M</t>
+  </si>
+  <si>
+    <t>EEPROM_MISO</t>
+  </si>
+  <si>
+    <t>MISO_M</t>
+  </si>
+  <si>
+    <t>SEE LRCLK_OUT0</t>
+  </si>
+  <si>
+    <t>DSP_LED0</t>
+  </si>
+  <si>
+    <t>DSP_LED1</t>
+  </si>
+  <si>
+    <t>SEE LRCLK_IN0</t>
+  </si>
+  <si>
+    <t>SEE LRCLK_IN1</t>
+  </si>
+  <si>
+    <t>ADC</t>
+  </si>
+  <si>
+    <t>DAC SIGNAL</t>
+  </si>
+  <si>
+    <t>MCLK</t>
+  </si>
+  <si>
+    <t>BICK</t>
+  </si>
+  <si>
+    <t>LRCK</t>
+  </si>
+  <si>
+    <t>SDTI1</t>
+  </si>
+  <si>
+    <t>DAC_MCLK</t>
+  </si>
+  <si>
+    <t>LDOE</t>
+  </si>
+  <si>
+    <t>HIGH</t>
+  </si>
+  <si>
+    <t>PDN</t>
+  </si>
+  <si>
+    <t>I2C</t>
+  </si>
+  <si>
+    <t>LOW = POWER DOWN</t>
+  </si>
+  <si>
+    <t>PARALLEL CONTROL</t>
+  </si>
+  <si>
+    <t>DIF</t>
+  </si>
+  <si>
+    <t>TDM1</t>
+  </si>
+  <si>
+    <t>TDM0</t>
+  </si>
+  <si>
+    <t>DCHAIN</t>
+  </si>
+  <si>
+    <t>LOW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32b I2S, "NORMAL" </t>
+  </si>
+  <si>
+    <t>PS</t>
+  </si>
+  <si>
+    <t>BICK/DCLK</t>
+  </si>
+  <si>
+    <t>STDO1</t>
+  </si>
+  <si>
+    <t>ADC_MCLK</t>
+  </si>
+  <si>
+    <t>ADC_BCK</t>
+  </si>
+  <si>
+    <t>MSN</t>
+  </si>
+  <si>
+    <t>CKS0</t>
+  </si>
+  <si>
+    <t>CKS1</t>
+  </si>
+  <si>
+    <t>CKS2</t>
+  </si>
+  <si>
+    <t>CKS3</t>
+  </si>
+  <si>
+    <t>SLOW</t>
+  </si>
+  <si>
+    <t>SD</t>
+  </si>
+  <si>
+    <t>DIF0</t>
+  </si>
+  <si>
+    <t>DIF1</t>
+  </si>
+  <si>
+    <t>HPFE</t>
+  </si>
+  <si>
+    <t>ODP</t>
+  </si>
+  <si>
+    <t>INTERNAL LDO</t>
+  </si>
+  <si>
+    <t>SLAVE MODE</t>
+  </si>
+  <si>
+    <t>12M NORMAL SPEED</t>
+  </si>
+  <si>
+    <t>256fs</t>
+  </si>
+  <si>
+    <t>32 BIT I2S</t>
+  </si>
+  <si>
+    <t>PW0</t>
+  </si>
+  <si>
+    <t>PW1</t>
+  </si>
+  <si>
+    <t>PW2</t>
+  </si>
+  <si>
+    <t>OPTIMAL DATA PLACEMENT</t>
+  </si>
+  <si>
+    <t>BOTH CHANNELS ON</t>
+  </si>
+  <si>
+    <t>SLOT 2 = CH2</t>
+  </si>
+  <si>
+    <t>SLOT 1 = CH1</t>
+  </si>
+  <si>
+    <t>1Hz HP filter</t>
+  </si>
+  <si>
+    <t>SLOW ROLL OFF</t>
   </si>
 </sst>
 </file>
@@ -1919,7 +2111,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>175</v>
+        <v>146</v>
       </c>
       <c r="C2" t="s">
         <v>5</v>
@@ -1939,7 +2131,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>154</v>
+        <v>125</v>
       </c>
       <c r="C3" t="s">
         <v>65</v>
@@ -1960,7 +2152,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>154</v>
+        <v>125</v>
       </c>
       <c r="C4" t="s">
         <v>65</v>
@@ -1981,7 +2173,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>155</v>
+        <v>126</v>
       </c>
       <c r="C5" t="s">
         <v>65</v>
@@ -2002,7 +2194,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>155</v>
+        <v>126</v>
       </c>
       <c r="C6" t="s">
         <v>65</v>
@@ -2023,7 +2215,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>157</v>
+        <v>128</v>
       </c>
       <c r="C7" t="s">
         <v>66</v>
@@ -2044,7 +2236,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>158</v>
+        <v>129</v>
       </c>
       <c r="C8" t="s">
         <v>66</v>
@@ -2059,7 +2251,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>156</v>
+        <v>127</v>
       </c>
       <c r="C9" t="s">
         <v>66</v>
@@ -2080,7 +2272,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>156</v>
+        <v>127</v>
       </c>
       <c r="C10" t="s">
         <v>66</v>
@@ -2101,7 +2293,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>156</v>
+        <v>127</v>
       </c>
       <c r="C11" t="s">
         <v>66</v>
@@ -2122,7 +2314,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>156</v>
+        <v>127</v>
       </c>
       <c r="C12" t="s">
         <v>66</v>
@@ -2143,13 +2335,13 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>186</v>
+        <v>157</v>
       </c>
       <c r="C13" t="s">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="D13" t="s">
-        <v>195</v>
+        <v>166</v>
       </c>
       <c r="E13">
         <v>5</v>
@@ -2165,12 +2357,12 @@
         <v>74</v>
       </c>
       <c r="I13" t="s">
-        <v>188</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="D14" t="s">
         <v>42</v>
@@ -2186,21 +2378,21 @@
         <v>33</v>
       </c>
       <c r="H14" t="s">
-        <v>187</v>
+        <v>158</v>
       </c>
       <c r="I14" t="s">
-        <v>189</v>
+        <v>160</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>190</v>
+        <v>161</v>
       </c>
       <c r="C15" t="s">
-        <v>192</v>
+        <v>163</v>
       </c>
       <c r="D15" t="s">
-        <v>195</v>
+        <v>166</v>
       </c>
       <c r="E15">
         <v>5</v>
@@ -2216,12 +2408,12 @@
         <v>74</v>
       </c>
       <c r="I15" t="s">
-        <v>188</v>
+        <v>159</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C16" t="s">
-        <v>192</v>
+        <v>163</v>
       </c>
       <c r="D16" t="s">
         <v>42</v>
@@ -2237,18 +2429,18 @@
         <v>46.199999999999996</v>
       </c>
       <c r="H16" t="s">
-        <v>187</v>
+        <v>158</v>
       </c>
       <c r="I16" t="s">
-        <v>189</v>
+        <v>160</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>197</v>
+        <v>168</v>
       </c>
       <c r="C17" t="s">
-        <v>193</v>
+        <v>164</v>
       </c>
       <c r="D17" t="s">
         <v>41</v>
@@ -2273,10 +2465,10 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C18" t="s">
-        <v>193</v>
+        <v>164</v>
       </c>
       <c r="D18" t="s">
-        <v>194</v>
+        <v>165</v>
       </c>
       <c r="E18">
         <v>1.2</v>
@@ -2297,7 +2489,7 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C19" t="s">
-        <v>193</v>
+        <v>164</v>
       </c>
       <c r="D19" t="s">
         <v>41</v>
@@ -2322,7 +2514,7 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C20" t="s">
-        <v>193</v>
+        <v>164</v>
       </c>
       <c r="D20" t="s">
         <v>42</v>
@@ -2421,13 +2613,13 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>178</v>
+        <v>149</v>
       </c>
       <c r="B26" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="C26" t="s">
-        <v>176</v>
+        <v>147</v>
       </c>
       <c r="D26" t="s">
         <v>42</v>
@@ -2505,12 +2697,12 @@
         <v>58</v>
       </c>
       <c r="M39" t="s">
-        <v>160</v>
+        <v>131</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>184</v>
+        <v>155</v>
       </c>
       <c r="C40" t="s">
         <v>51</v>
@@ -2545,7 +2737,7 @@
     </row>
     <row r="41" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>184</v>
+        <v>155</v>
       </c>
       <c r="C41" t="s">
         <v>51</v>
@@ -2580,7 +2772,7 @@
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
-        <v>185</v>
+        <v>156</v>
       </c>
       <c r="C42" t="s">
         <v>51</v>
@@ -2615,7 +2807,7 @@
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>185</v>
+        <v>156</v>
       </c>
       <c r="C43" t="s">
         <v>51</v>
@@ -2676,10 +2868,10 @@
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>179</v>
+        <v>150</v>
       </c>
       <c r="C45" t="s">
-        <v>168</v>
+        <v>139</v>
       </c>
       <c r="D45" t="s">
         <v>38</v>
@@ -2711,10 +2903,10 @@
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
-        <v>181</v>
+        <v>152</v>
       </c>
       <c r="C46" t="s">
-        <v>168</v>
+        <v>139</v>
       </c>
       <c r="D46" t="s">
         <v>42</v>
@@ -2746,10 +2938,10 @@
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="C47" t="s">
-        <v>196</v>
+        <v>167</v>
       </c>
       <c r="D47" t="s">
         <v>41</v>
@@ -2781,13 +2973,13 @@
     </row>
     <row r="48" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
-        <v>183</v>
+        <v>154</v>
       </c>
       <c r="C48" t="s">
         <v>71</v>
       </c>
       <c r="D48" t="s">
-        <v>194</v>
+        <v>165</v>
       </c>
       <c r="E48">
         <v>3.3</v>
@@ -2823,13 +3015,13 @@
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>182</v>
+        <v>153</v>
       </c>
       <c r="C49" t="s">
-        <v>196</v>
+        <v>167</v>
       </c>
       <c r="D49" t="s">
-        <v>195</v>
+        <v>166</v>
       </c>
       <c r="E49">
         <v>5.5</v>
@@ -2866,7 +3058,7 @@
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C53" t="s">
-        <v>159</v>
+        <v>130</v>
       </c>
       <c r="D53" t="s">
         <v>84</v>
@@ -2935,7 +3127,7 @@
     </row>
     <row r="58" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
-        <v>184</v>
+        <v>155</v>
       </c>
       <c r="C58" t="s">
         <v>73</v>
@@ -2954,7 +3146,7 @@
     </row>
     <row r="59" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
-        <v>185</v>
+        <v>156</v>
       </c>
       <c r="D59" t="s">
         <v>63</v>
@@ -2970,7 +3162,7 @@
     </row>
     <row r="61" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
-        <v>184</v>
+        <v>155</v>
       </c>
       <c r="C61" t="s">
         <v>72</v>
@@ -2989,7 +3181,7 @@
     </row>
     <row r="62" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
-        <v>185</v>
+        <v>156</v>
       </c>
       <c r="D62" t="s">
         <v>64</v>
@@ -3007,7 +3199,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
@@ -3016,159 +3208,519 @@
     <col min="4" max="4" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E1" t="s">
+        <v>213</v>
+      </c>
+      <c r="I1" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E2" t="s">
+        <v>215</v>
+      </c>
+      <c r="F2" t="s">
+        <v>235</v>
+      </c>
+      <c r="I2" t="s">
+        <v>215</v>
+      </c>
+      <c r="J2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B3" t="s">
+        <v>174</v>
+      </c>
+      <c r="E3" t="s">
+        <v>233</v>
+      </c>
+      <c r="F3" t="s">
+        <v>236</v>
+      </c>
+      <c r="I3" t="s">
+        <v>216</v>
+      </c>
+      <c r="J3" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B4" t="s">
+        <v>175</v>
+      </c>
+      <c r="E4" t="s">
+        <v>234</v>
+      </c>
+      <c r="F4" t="s">
+        <v>188</v>
+      </c>
+      <c r="I4" t="s">
+        <v>217</v>
+      </c>
+      <c r="J4" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B5" t="s">
+        <v>176</v>
+      </c>
+      <c r="E5" t="s">
+        <v>217</v>
+      </c>
+      <c r="F5" t="s">
+        <v>187</v>
+      </c>
+      <c r="I5" t="s">
+        <v>218</v>
+      </c>
+      <c r="J5" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>177</v>
+      </c>
+      <c r="B6" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>178</v>
+      </c>
+      <c r="B7" t="s">
+        <v>179</v>
+      </c>
+      <c r="E7" t="s">
+        <v>220</v>
+      </c>
+      <c r="F7" t="s">
+        <v>221</v>
+      </c>
+      <c r="G7" t="s">
+        <v>248</v>
+      </c>
+      <c r="I7" t="s">
+        <v>220</v>
+      </c>
+      <c r="J7" t="s">
+        <v>221</v>
+      </c>
+      <c r="K7" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E8" t="s">
+        <v>222</v>
+      </c>
+      <c r="I8" t="s">
+        <v>222</v>
+      </c>
+      <c r="K8" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>181</v>
+      </c>
+      <c r="B9" t="s">
+        <v>186</v>
+      </c>
+      <c r="E9" t="s">
+        <v>237</v>
+      </c>
+      <c r="F9" t="s">
+        <v>230</v>
+      </c>
+      <c r="G9" t="s">
+        <v>249</v>
+      </c>
+      <c r="I9" t="s">
+        <v>223</v>
+      </c>
+      <c r="J9" t="s">
+        <v>221</v>
+      </c>
+      <c r="K9" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>182</v>
+      </c>
+      <c r="B10" t="s">
+        <v>187</v>
+      </c>
+      <c r="E10" t="s">
+        <v>238</v>
+      </c>
+      <c r="F10" t="s">
+        <v>230</v>
+      </c>
+      <c r="G10" t="s">
+        <v>250</v>
+      </c>
+      <c r="I10" t="s">
+        <v>232</v>
+      </c>
+      <c r="J10" t="s">
+        <v>221</v>
+      </c>
+      <c r="K10" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>183</v>
+      </c>
+      <c r="B11" t="s">
+        <v>188</v>
+      </c>
+      <c r="E11" t="s">
+        <v>239</v>
+      </c>
+      <c r="F11" t="s">
+        <v>221</v>
+      </c>
+      <c r="G11" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E12" t="s">
+        <v>240</v>
+      </c>
+      <c r="F12" t="s">
+        <v>230</v>
+      </c>
+      <c r="I12" t="s">
+        <v>226</v>
+      </c>
+      <c r="J12" t="s">
+        <v>221</v>
+      </c>
+      <c r="K12" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>184</v>
+      </c>
+      <c r="B13" t="s">
+        <v>189</v>
+      </c>
+      <c r="E13" t="s">
+        <v>241</v>
+      </c>
+      <c r="F13" t="s">
+        <v>230</v>
+      </c>
+      <c r="I13" t="s">
+        <v>227</v>
+      </c>
+      <c r="J13" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>185</v>
+      </c>
+      <c r="B14" t="s">
+        <v>190</v>
+      </c>
+      <c r="E14" t="s">
+        <v>242</v>
+      </c>
+      <c r="F14" t="s">
+        <v>221</v>
+      </c>
+      <c r="G14" t="s">
+        <v>261</v>
+      </c>
+      <c r="I14" t="s">
+        <v>228</v>
+      </c>
+      <c r="J14" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>98</v>
+      </c>
+      <c r="B15" t="s">
+        <v>191</v>
+      </c>
+      <c r="E15" t="s">
+        <v>243</v>
+      </c>
+      <c r="F15" t="s">
+        <v>230</v>
+      </c>
+      <c r="G15" t="s">
+        <v>261</v>
+      </c>
+      <c r="I15" t="s">
+        <v>229</v>
+      </c>
+      <c r="J15" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E16" t="s">
+        <v>244</v>
+      </c>
+      <c r="F16" t="s">
+        <v>221</v>
+      </c>
+      <c r="G16" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>192</v>
+      </c>
+      <c r="B17" t="s">
+        <v>195</v>
+      </c>
+      <c r="E17" t="s">
+        <v>245</v>
+      </c>
+      <c r="F17" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>193</v>
+      </c>
+      <c r="B18" t="s">
+        <v>196</v>
+      </c>
+      <c r="E18" t="s">
+        <v>228</v>
+      </c>
+      <c r="F18" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>194</v>
+      </c>
+      <c r="B19" t="s">
+        <v>197</v>
+      </c>
+      <c r="E19" t="s">
+        <v>227</v>
+      </c>
+      <c r="F19" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E20" t="s">
+        <v>246</v>
+      </c>
+      <c r="F20" t="s">
+        <v>221</v>
+      </c>
+      <c r="G20" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>85</v>
       </c>
-      <c r="B1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C1" t="s">
-        <v>110</v>
-      </c>
-      <c r="D1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="B21" t="s">
+        <v>200</v>
+      </c>
+      <c r="C21" t="s">
+        <v>201</v>
+      </c>
+      <c r="E21" t="s">
+        <v>247</v>
+      </c>
+      <c r="F21" t="s">
+        <v>221</v>
+      </c>
+      <c r="G21" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>86</v>
       </c>
-      <c r="B2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B22" t="s">
+        <v>202</v>
+      </c>
+      <c r="C22" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>87</v>
       </c>
-      <c r="B3" t="s">
-        <v>108</v>
-      </c>
-      <c r="D3" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="B23" t="s">
+        <v>204</v>
+      </c>
+      <c r="C23" t="s">
+        <v>205</v>
+      </c>
+      <c r="E23" t="s">
+        <v>253</v>
+      </c>
+      <c r="F23" t="s">
+        <v>230</v>
+      </c>
+      <c r="G23" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>88</v>
       </c>
-      <c r="B4" t="s">
-        <v>111</v>
-      </c>
-      <c r="C4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B24" t="s">
+        <v>206</v>
+      </c>
+      <c r="C24" t="s">
+        <v>207</v>
+      </c>
+      <c r="E24" t="s">
+        <v>254</v>
+      </c>
+      <c r="F24" t="s">
+        <v>230</v>
+      </c>
+      <c r="G24" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>89</v>
       </c>
-      <c r="B5" t="s">
-        <v>112</v>
-      </c>
-      <c r="C5" t="s">
-        <v>99</v>
-      </c>
-      <c r="D5" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="B25" t="s">
+        <v>208</v>
+      </c>
+      <c r="E25" t="s">
+        <v>255</v>
+      </c>
+      <c r="F25" t="s">
+        <v>221</v>
+      </c>
+      <c r="G25" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>90</v>
       </c>
-      <c r="B6" t="s">
-        <v>113</v>
-      </c>
-      <c r="D6" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="B26" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>91</v>
       </c>
-      <c r="B7" t="s">
-        <v>114</v>
-      </c>
-      <c r="D7" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="B27" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>92</v>
       </c>
-      <c r="B8" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="B28" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>93</v>
       </c>
-      <c r="B9" t="s">
-        <v>116</v>
-      </c>
-      <c r="D9" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="B29" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>94</v>
       </c>
-      <c r="B10" t="s">
-        <v>117</v>
-      </c>
-      <c r="C10" t="s">
-        <v>100</v>
-      </c>
-      <c r="D10" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="B30" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>95</v>
       </c>
-      <c r="B11" t="s">
-        <v>118</v>
-      </c>
-      <c r="C11" t="s">
-        <v>101</v>
-      </c>
-      <c r="D11" t="s">
-        <v>106</v>
-      </c>
-      <c r="E11" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="B31" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>96</v>
       </c>
-      <c r="B12" t="s">
-        <v>119</v>
-      </c>
-      <c r="D12" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B13" t="s">
-        <v>120</v>
-      </c>
-      <c r="D13" t="s">
-        <v>122</v>
+      <c r="B32" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>198</v>
+      </c>
+      <c r="B33" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>199</v>
+      </c>
+      <c r="B34" t="s">
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -3187,7 +3739,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>141</v>
+        <v>112</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -3201,24 +3753,24 @@
         <v>51</v>
       </c>
       <c r="D2" t="s">
-        <v>128</v>
+        <v>99</v>
       </c>
       <c r="E2">
         <v>1.19</v>
       </c>
       <c r="F2" t="s">
-        <v>129</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="B3" t="s">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="D3" t="s">
-        <v>132</v>
+        <v>103</v>
       </c>
       <c r="G3">
         <f>$E$2*(1+E6/E7)</f>
@@ -3227,13 +3779,13 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>133</v>
+        <v>104</v>
       </c>
       <c r="B4" t="s">
-        <v>134</v>
+        <v>105</v>
       </c>
       <c r="D4" t="s">
-        <v>135</v>
+        <v>106</v>
       </c>
       <c r="G4">
         <f>E2*(-E8/E9)</f>
@@ -3242,51 +3794,51 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D6" t="s">
-        <v>136</v>
+        <v>107</v>
       </c>
       <c r="E6">
         <v>32400</v>
       </c>
       <c r="F6" t="s">
-        <v>137</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D7" t="s">
-        <v>138</v>
+        <v>109</v>
       </c>
       <c r="E7">
         <v>10000</v>
       </c>
       <c r="F7" t="s">
-        <v>137</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D8" t="s">
-        <v>139</v>
+        <v>110</v>
       </c>
       <c r="E8">
         <v>42200</v>
       </c>
       <c r="F8" t="s">
-        <v>137</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D9" t="s">
-        <v>140</v>
+        <v>111</v>
       </c>
       <c r="E9">
         <v>10000</v>
       </c>
       <c r="F9" t="s">
-        <v>137</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>142</v>
+        <v>113</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -3300,24 +3852,24 @@
         <v>51</v>
       </c>
       <c r="D12" t="s">
-        <v>128</v>
+        <v>99</v>
       </c>
       <c r="E12">
         <v>1.19</v>
       </c>
       <c r="F12" t="s">
-        <v>129</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="B13" t="s">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="D13" t="s">
-        <v>132</v>
+        <v>103</v>
       </c>
       <c r="G13">
         <f>$E$2*(1+E16/E17)</f>
@@ -3326,13 +3878,13 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>133</v>
+        <v>104</v>
       </c>
       <c r="B14" t="s">
-        <v>134</v>
+        <v>105</v>
       </c>
       <c r="D14" t="s">
-        <v>135</v>
+        <v>106</v>
       </c>
       <c r="G14">
         <f>E12*(-E18/E19)</f>
@@ -3341,51 +3893,51 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D16" t="s">
-        <v>136</v>
+        <v>107</v>
       </c>
       <c r="E16">
         <v>75000</v>
       </c>
       <c r="F16" t="s">
-        <v>137</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D17" t="s">
-        <v>138</v>
+        <v>109</v>
       </c>
       <c r="E17">
         <v>10000</v>
       </c>
       <c r="F17" t="s">
-        <v>137</v>
+        <v>108</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D18" t="s">
-        <v>139</v>
+        <v>110</v>
       </c>
       <c r="E18">
         <v>84500</v>
       </c>
       <c r="F18" t="s">
-        <v>137</v>
+        <v>108</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D19" t="s">
-        <v>140</v>
+        <v>111</v>
       </c>
       <c r="E19">
         <v>10000</v>
       </c>
       <c r="F19" t="s">
-        <v>137</v>
+        <v>108</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>145</v>
+        <v>116</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -3396,27 +3948,27 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>146</v>
+        <v>117</v>
       </c>
       <c r="D23" t="s">
-        <v>149</v>
+        <v>120</v>
       </c>
       <c r="E23">
         <v>1.2130000000000001</v>
       </c>
       <c r="F23" t="s">
-        <v>129</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="B24" t="s">
-        <v>148</v>
+        <v>119</v>
       </c>
       <c r="D24" t="s">
-        <v>150</v>
+        <v>121</v>
       </c>
       <c r="G24">
         <f>E29/E30*E23+1</f>
@@ -3425,13 +3977,13 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>147</v>
+        <v>118</v>
       </c>
       <c r="B25" t="s">
         <v>72</v>
       </c>
       <c r="D25" t="s">
-        <v>153</v>
+        <v>124</v>
       </c>
       <c r="G25">
         <f>E31/(-E32)*E23</f>
@@ -3440,73 +3992,73 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D29" t="s">
-        <v>143</v>
+        <v>114</v>
       </c>
       <c r="E29">
         <v>1000000</v>
       </c>
       <c r="F29" t="s">
-        <v>137</v>
+        <v>108</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D30" t="s">
-        <v>144</v>
+        <v>115</v>
       </c>
       <c r="E30">
         <v>110000</v>
       </c>
       <c r="F30" t="s">
-        <v>137</v>
+        <v>108</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D31" t="s">
-        <v>151</v>
+        <v>122</v>
       </c>
       <c r="E31">
         <v>1000000</v>
       </c>
       <c r="F31" t="s">
-        <v>137</v>
+        <v>108</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D32" t="s">
-        <v>152</v>
+        <v>123</v>
       </c>
       <c r="E32">
         <v>100000</v>
       </c>
       <c r="F32" t="s">
-        <v>137</v>
+        <v>108</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>168</v>
+        <v>139</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>161</v>
+        <v>132</v>
       </c>
       <c r="B36">
         <v>5</v>
       </c>
       <c r="D36" t="s">
-        <v>149</v>
+        <v>120</v>
       </c>
       <c r="E36">
         <v>0.65</v>
       </c>
       <c r="F36" t="s">
-        <v>129</v>
+        <v>100</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="D37" t="s">
-        <v>169</v>
+        <v>140</v>
       </c>
       <c r="G37">
         <f>E36*(1+E40/E41)</f>
@@ -3515,14 +4067,14 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="D38" t="s">
-        <v>164</v>
+        <v>135</v>
       </c>
       <c r="E38">
         <f>G38</f>
         <v>1E-8</v>
       </c>
       <c r="F38" t="s">
-        <v>165</v>
+        <v>136</v>
       </c>
       <c r="G38">
         <v>1E-8</v>
@@ -3530,44 +4082,44 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C40" t="s">
-        <v>163</v>
+        <v>134</v>
       </c>
       <c r="D40" t="s">
-        <v>143</v>
+        <v>114</v>
       </c>
       <c r="E40">
         <v>1000000</v>
       </c>
       <c r="F40" t="s">
-        <v>171</v>
+        <v>142</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C41" t="s">
-        <v>162</v>
+        <v>133</v>
       </c>
       <c r="D41" t="s">
-        <v>144</v>
+        <v>115</v>
       </c>
       <c r="E41">
         <v>150000</v>
       </c>
       <c r="F41" t="s">
-        <v>172</v>
+        <v>143</v>
       </c>
       <c r="G41" t="s">
-        <v>166</v>
+        <v>137</v>
       </c>
       <c r="H41">
         <v>10</v>
       </c>
       <c r="I41" t="s">
-        <v>167</v>
+        <v>138</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="D42" t="s">
-        <v>170</v>
+        <v>141</v>
       </c>
       <c r="E42" s="2">
         <f>E40+E41</f>
@@ -3580,29 +4132,29 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>168</v>
+        <v>139</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>161</v>
+        <v>132</v>
       </c>
       <c r="B44">
         <v>3.3</v>
       </c>
       <c r="D44" t="s">
-        <v>149</v>
+        <v>120</v>
       </c>
       <c r="E44">
         <v>0.65</v>
       </c>
       <c r="F44" t="s">
-        <v>129</v>
+        <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="D45" t="s">
-        <v>169</v>
+        <v>140</v>
       </c>
       <c r="G45">
         <f>E44*(1+E48/E49)</f>
@@ -3611,14 +4163,14 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="D46" t="s">
-        <v>164</v>
+        <v>135</v>
       </c>
       <c r="E46">
         <f>G46</f>
         <v>1E-8</v>
       </c>
       <c r="F46" t="s">
-        <v>165</v>
+        <v>136</v>
       </c>
       <c r="G46">
         <v>1E-8</v>
@@ -3626,44 +4178,44 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C48" t="s">
-        <v>163</v>
+        <v>134</v>
       </c>
       <c r="D48" t="s">
-        <v>143</v>
+        <v>114</v>
       </c>
       <c r="E48">
         <v>1000000</v>
       </c>
       <c r="F48" t="s">
-        <v>171</v>
+        <v>142</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C49" t="s">
-        <v>162</v>
+        <v>133</v>
       </c>
       <c r="D49" t="s">
-        <v>144</v>
+        <v>115</v>
       </c>
       <c r="E49">
         <v>245000</v>
       </c>
       <c r="F49" t="s">
-        <v>173</v>
+        <v>144</v>
       </c>
       <c r="G49" t="s">
-        <v>166</v>
+        <v>137</v>
       </c>
       <c r="H49">
         <v>10</v>
       </c>
       <c r="I49" t="s">
-        <v>167</v>
+        <v>138</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="D50" t="s">
-        <v>170</v>
+        <v>141</v>
       </c>
       <c r="E50" s="2">
         <f>E48+E49</f>
@@ -3676,29 +4228,29 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>168</v>
+        <v>139</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>161</v>
+        <v>132</v>
       </c>
       <c r="B53">
         <v>1.8</v>
       </c>
       <c r="D53" t="s">
-        <v>149</v>
+        <v>120</v>
       </c>
       <c r="E53">
         <v>0.65</v>
       </c>
       <c r="F53" t="s">
-        <v>129</v>
+        <v>100</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="D54" t="s">
-        <v>169</v>
+        <v>140</v>
       </c>
       <c r="G54">
         <f>E53*(1+E57/E58)</f>
@@ -3707,14 +4259,14 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="D55" t="s">
-        <v>164</v>
+        <v>135</v>
       </c>
       <c r="E55">
         <f>G55</f>
         <v>1E-8</v>
       </c>
       <c r="F55" t="s">
-        <v>165</v>
+        <v>136</v>
       </c>
       <c r="G55">
         <v>1E-8</v>
@@ -3722,44 +4274,44 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C57" t="s">
-        <v>163</v>
+        <v>134</v>
       </c>
       <c r="D57" t="s">
-        <v>143</v>
+        <v>114</v>
       </c>
       <c r="E57">
         <v>1000000</v>
       </c>
       <c r="F57" t="s">
-        <v>171</v>
+        <v>142</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C58" t="s">
-        <v>162</v>
+        <v>133</v>
       </c>
       <c r="D58" t="s">
-        <v>144</v>
+        <v>115</v>
       </c>
       <c r="E58">
         <v>560000</v>
       </c>
       <c r="F58" t="s">
-        <v>174</v>
+        <v>145</v>
       </c>
       <c r="G58" t="s">
-        <v>166</v>
+        <v>137</v>
       </c>
       <c r="H58">
         <v>10</v>
       </c>
       <c r="I58" t="s">
-        <v>167</v>
+        <v>138</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="D59" t="s">
-        <v>170</v>
+        <v>141</v>
       </c>
       <c r="E59" s="2">
         <f>E57+E58</f>
